--- a/metrics/Global_Metrics_Ablation_Study_RHm_VPD.xlsx
+++ b/metrics/Global_Metrics_Ablation_Study_RHm_VPD.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:AS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,60 +471,180 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>MAE_constant</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_constant</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_constant</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_constant</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2_constant</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_constant</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_constant</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_constant</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_stepwise</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_stepwise</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_stepwise</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_stepwise</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2_stepwise</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_stepwise</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_stepwise</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_stepwise</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>R2_dynamic</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_dynamic</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_dynamic</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_dynamic</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Int_Conf_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_RMSE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Pearson</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Spearman</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Kendall</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MAE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MedAE</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Max_Step</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Pred_Step</t>
         </is>
@@ -535,67 +655,139 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.650858997144548</v>
+        <v>2.482307546394207</v>
       </c>
       <c r="C2" t="n">
-        <v>2.535079625040606</v>
+        <v>2.351899405154693</v>
       </c>
       <c r="D2" t="n">
-        <v>9.399165941939877</v>
+        <v>8.464475001681643</v>
       </c>
       <c r="E2" t="n">
-        <v>3.065805920462004</v>
+        <v>2.909377081383856</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8821152930358382</v>
+        <v>0.9049294258246757</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9392750694497679</v>
+        <v>0.9513552492097866</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9395036049989622</v>
+        <v>0.9513896356782682</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7944074119188291</v>
+        <v>0.8181444438212953</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01196113531787735</v>
+        <v>3.110837597846138</v>
       </c>
       <c r="K2" t="n">
-        <v>0.149173351496722</v>
+        <v>3.329313804754525</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4730732728306098</v>
+        <v>11.99341515127565</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4744136881132649</v>
+        <v>3.46315104367044</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3987423180562791</v>
+        <v>0.8711501868278747</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1214575739385801</v>
+        <v>0.9792034049233819</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1233138762706025</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+        <v>0.9835631609212711</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.9064356785486295</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.284823734357548</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.300561170888929</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6.372217557815627</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.524325168795737</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.9139777511647651</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9565800444908732</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.952193680985515</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.8185063610002397</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.371262192697963</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.039996829794593</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>8.426203674212363</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.90279239254418</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.8997028940899272</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.9579030991302028</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.9587598007115472</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8359121607427893</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.01507032713503059</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.2068634571772701</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.007728734187233466</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.009357246152555898</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.01609823080691147</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.184799060724778</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.2096753079303062</v>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="AQ2" t="n">
         <v>3</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AR2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AS2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -604,67 +796,139 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3154969086728594</v>
+        <v>0.3357820388179244</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2145825959029561</v>
+        <v>0.2144185735277039</v>
       </c>
       <c r="D3" t="n">
-        <v>0.200630897241943</v>
+        <v>0.2281485427733648</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4479184046698048</v>
+        <v>0.4776489744293029</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9642190958066502</v>
+        <v>0.9635998379452972</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9844193474119806</v>
+        <v>0.9836364447633771</v>
       </c>
       <c r="H3" t="n">
-        <v>0.987702725486341</v>
+        <v>0.9853836913560228</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9060165867959509</v>
+        <v>0.8994888934225069</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004935400655553701</v>
+        <v>0.1853457324358064</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02899188079084614</v>
+        <v>0.1388319704553682</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4922207387997442</v>
+        <v>0.05571872543396961</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4924394952018735</v>
+        <v>0.2360481421955479</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4483952650655731</v>
+        <v>0.9900050022133864</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0216692251360639</v>
+        <v>0.9970262358888905</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02037193700464983</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+        <v>0.9959817326522119</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.9586474811043704</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.2327669041855355</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1603855372609129</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.1019745522286197</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.3193345459367334</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.9655114188716678</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9874016212228215</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.9842007588628322</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.8930111832867317</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.4517844121596202</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.3410367440104469</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.3659290327085305</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6049206829895392</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.9474063316713879</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.982988842229686</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.9873406956757032</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.9070855577991779</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.007899715636706384</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.05585081529412664</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.003570098215228745</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.004286289657941533</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.01392478378959344</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.04295737334342839</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.04295979460618377</v>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="AQ3" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AR3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AS3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -673,67 +937,139 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.086253520862164</v>
+        <v>1.118613075425997</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7651093121464778</v>
+        <v>0.6739182438381128</v>
       </c>
       <c r="D4" t="n">
-        <v>2.383915121709683</v>
+        <v>2.66054628898357</v>
       </c>
       <c r="E4" t="n">
-        <v>1.543993238880819</v>
+        <v>1.631118110065476</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9623559580668718</v>
+        <v>0.9623664699159885</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9810042559187223</v>
+        <v>0.9811047994784142</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9797787117635408</v>
+        <v>0.9763813096288553</v>
       </c>
       <c r="I4" t="n">
-        <v>0.883942349497351</v>
+        <v>0.8767049238263855</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005590388785116862</v>
+        <v>1.32745033617543</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1152695216605667</v>
+        <v>1.180317184404415</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4917682492033603</v>
+        <v>2.789041180318244</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4875408724068805</v>
+        <v>1.670042269021429</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4353757359820283</v>
+        <v>0.9668771305480128</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08217185878581634</v>
+        <v>0.9845414361315994</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1085360096434427</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+        <v>0.9825583948510397</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.9094986426754653</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.230713485370367</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.6594754806118317</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.74003930636162</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.933918122972537</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.9083386624629151</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9611552077597754</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.9519900423292152</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.8369119373313829</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.9759678771700493</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.606564285687254</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.971477921463362</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.404093273776127</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.974753975490691</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.9873863550754014</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.9834383593233634</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8979286835992561</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.01054875629488838</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.2119889690680498</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.005309355024997076</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.007365518532282567</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.01804354233665467</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.1414404595714162</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.1031062052723421</v>
+      </c>
+      <c r="AO4" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="AQ4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AR4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AS4" t="n">
         <v>1</v>
       </c>
     </row>
